--- a/enquadramentos.xlsx
+++ b/enquadramentos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEGUR\Desktop\divprom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel\Desktop\divprom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF66A64-598A-4241-AC85-13BEFE7DA3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF2C726-965C-4825-B8A2-01161AAD58DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4530" windowWidth="28800" windowHeight="8235" xr2:uid="{44A2A837-6D6A-4BAB-A0D4-8995776C34B6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{44A2A837-6D6A-4BAB-A0D4-8995776C34B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -624,38 +624,21 @@
 além das penalidades em que incorre, as estabelecidas no art. 210</t>
   </si>
   <si>
-    <t xml:space="preserve">amparo_legal	</t>
-  </si>
-  <si>
     <t>descricao_infracao</t>
   </si>
   <si>
     <t>codigo</t>
+  </si>
+  <si>
+    <t>amparo_legal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -671,18 +654,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -712,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -723,20 +700,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,9 +721,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -796,7 +761,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -902,7 +867,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1044,7 +1009,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1053,25 +1018,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6936F087-65E9-41AB-AB9D-A22BB1ECBC77}">
   <dimension ref="A1:C77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="140" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1082,18 +1047,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1104,7 +1069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1115,7 +1080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1126,18 +1091,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -1148,7 +1113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -1159,7 +1124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -1170,7 +1135,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -1181,7 +1146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -1192,7 +1157,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
@@ -1203,7 +1168,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -1214,7 +1179,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
@@ -1225,7 +1190,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
@@ -1236,7 +1201,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -1247,7 +1212,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
@@ -1258,7 +1223,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
@@ -1269,7 +1234,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
@@ -1280,7 +1245,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>52</v>
       </c>
@@ -1291,7 +1256,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>55</v>
       </c>
@@ -1302,7 +1267,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -1313,7 +1278,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>59</v>
       </c>
@@ -1324,7 +1289,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>61</v>
       </c>
@@ -1335,7 +1300,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>62</v>
       </c>
@@ -1346,7 +1311,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
@@ -1357,7 +1322,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>65</v>
       </c>
@@ -1368,7 +1333,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>68</v>
       </c>
@@ -1379,7 +1344,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>71</v>
       </c>
@@ -1390,7 +1355,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>74</v>
       </c>
@@ -1401,7 +1366,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>77</v>
       </c>
@@ -1412,7 +1377,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
@@ -1423,7 +1388,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>83</v>
       </c>
@@ -1434,7 +1399,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>86</v>
       </c>
@@ -1445,7 +1410,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>89</v>
       </c>
@@ -1456,7 +1421,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>90</v>
       </c>
@@ -1467,7 +1432,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>92</v>
       </c>
@@ -1478,7 +1443,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>93</v>
       </c>
@@ -1489,7 +1454,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>94</v>
       </c>
@@ -1500,7 +1465,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>97</v>
       </c>
@@ -1511,7 +1476,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>100</v>
       </c>
@@ -1522,7 +1487,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>103</v>
       </c>
@@ -1533,7 +1498,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>105</v>
       </c>
@@ -1544,7 +1509,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>108</v>
       </c>
@@ -1555,7 +1520,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>111</v>
       </c>
@@ -1566,7 +1531,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>114</v>
       </c>
@@ -1577,7 +1542,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>117</v>
       </c>
@@ -1588,7 +1553,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>118</v>
       </c>
@@ -1599,7 +1564,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>120</v>
       </c>
@@ -1610,7 +1575,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>121</v>
       </c>
@@ -1621,7 +1586,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>122</v>
       </c>
@@ -1632,7 +1597,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>125</v>
       </c>
@@ -1643,7 +1608,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>128</v>
       </c>
@@ -1654,7 +1619,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>131</v>
       </c>
@@ -1665,7 +1630,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>134</v>
       </c>
@@ -1676,7 +1641,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>135</v>
       </c>
@@ -1687,7 +1652,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>138</v>
       </c>
@@ -1698,7 +1663,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>141</v>
       </c>
@@ -1709,7 +1674,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>144</v>
       </c>
@@ -1720,7 +1685,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>145</v>
       </c>
@@ -1731,7 +1696,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>148</v>
       </c>
@@ -1742,7 +1707,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>151</v>
       </c>
@@ -1753,7 +1718,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>152</v>
       </c>
@@ -1764,7 +1729,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>155</v>
       </c>
@@ -1775,7 +1740,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>157</v>
       </c>
@@ -1786,7 +1751,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>159</v>
       </c>
@@ -1797,7 +1762,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>161</v>
       </c>
@@ -1808,7 +1773,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>164</v>
       </c>
@@ -1819,7 +1784,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>165</v>
       </c>
@@ -1830,7 +1795,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>168</v>
       </c>
@@ -1841,7 +1806,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>171</v>
       </c>
@@ -1852,7 +1817,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>174</v>
       </c>
@@ -1863,7 +1828,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>177</v>
       </c>
@@ -1874,7 +1839,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>180</v>
       </c>
@@ -1885,7 +1850,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>182</v>
       </c>
@@ -1896,7 +1861,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>183</v>
       </c>
@@ -1909,6 +1874,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/enquadramentos.xlsx
+++ b/enquadramentos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel\Desktop\divprom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEGUR\Desktop\divprom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF2C726-965C-4825-B8A2-01161AAD58DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F94458-3B0C-412E-90B4-37C4CFC77B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{44A2A837-6D6A-4BAB-A0D4-8995776C34B6}"/>
+    <workbookView xWindow="0" yWindow="4530" windowWidth="28800" windowHeight="8235" xr2:uid="{44A2A837-6D6A-4BAB-A0D4-8995776C34B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="192">
   <si>
     <t>524-00</t>
   </si>
@@ -631,6 +631,15 @@
   </si>
   <si>
     <t>amparo_legal</t>
+  </si>
+  <si>
+    <t>000-00</t>
+  </si>
+  <si>
+    <t>Art. 279-A C.T.B.</t>
+  </si>
+  <si>
+    <t>Veículo abandonado.</t>
   </si>
 </sst>
 </file>
@@ -721,9 +730,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -761,7 +770,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -867,7 +876,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1009,7 +1018,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1017,15 +1026,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6936F087-65E9-41AB-AB9D-A22BB1ECBC77}">
-  <dimension ref="A1:C77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C78"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="140" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>187</v>
       </c>
@@ -1036,42 +1045,42 @@
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -1080,218 +1089,218 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>56</v>
@@ -1300,119 +1309,119 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>87</v>
@@ -1421,31 +1430,31 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>87</v>
@@ -1454,97 +1463,97 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+    <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>115</v>
@@ -1553,31 +1562,31 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
@@ -1586,53 +1595,53 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>132</v>
@@ -1641,42 +1650,42 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>142</v>
@@ -1685,31 +1694,31 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>149</v>
@@ -1718,64 +1727,64 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>162</v>
@@ -1784,75 +1793,75 @@
         <v>163</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+    <row r="73" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>178</v>
@@ -1861,14 +1870,25 @@
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>185</v>
       </c>
     </row>
